--- a/dataset/construct/dataset_splits/data_size/20_percent/merged/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/merged/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2246</v>
+        <v>474</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76.92898734377771</v>
+        <v>78.2075977577509</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E2" t="n">
-        <v>22.7244034844085</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I2" t="n">
+        <v>222</v>
+      </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K2" t="n">
-        <v>225.3</v>
+        <v>630</v>
       </c>
       <c r="L2" t="n">
-        <v>178.6</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>267.7</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>671.6</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>25.6</v>
+        <v>59</v>
       </c>
       <c r="P2" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>211.9</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>54.7</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>63.1</v>
+        <v>26.8</v>
       </c>
       <c r="V2" t="n">
-        <v>117.8</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X2" t="n">
-        <v>24.5</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.298611111111111</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.6052966641202</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.9831715115263</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -722,39 +709,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>168</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>983</v>
+        <v>2359</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +738,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.1668630694349</v>
+        <v>84.26097786270191</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>24.2214532871972</v>
       </c>
       <c r="E3" t="n">
-        <v>25.4580659041199</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>376.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1060</v>
+        <v>779</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>320.1</v>
       </c>
       <c r="K3" t="n">
-        <v>993</v>
+        <v>1475.4</v>
       </c>
       <c r="L3" t="n">
-        <v>491</v>
+        <v>140.7</v>
       </c>
       <c r="M3" t="n">
-        <v>960</v>
+        <v>42.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2444</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>227</v>
+        <v>272.6</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>34.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>370</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
-        <v>151</v>
+        <v>37.5</v>
       </c>
       <c r="T3" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>24.35</v>
       </c>
       <c r="V3" t="n">
-        <v>206</v>
+        <v>0.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.5734657499363</v>
       </c>
       <c r="X3" t="n">
-        <v>24.35</v>
+        <v>23.6975361509812</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.169172932330827</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.6921643870788</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -843,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -858,27 +834,18 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
         <v>136</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>501</v>
+        <v>365</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,40 +853,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.7024477463432</v>
+        <v>86.5307742033615</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>30.4878048780487</v>
       </c>
       <c r="E4" t="n">
-        <v>24.7675659198292</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="I4" t="n">
-        <v>983</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -937,34 +904,34 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X4" t="n">
-        <v>19.8</v>
+        <v>21.4950646217447</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.191780821917808</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.0534759358289</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.9279552640389</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -973,36 +940,25 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>132</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1010,79 +966,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.6452314814815</v>
+        <v>91.0289564795802</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>23.1111111111111</v>
       </c>
       <c r="E5" t="n">
-        <v>19.9510204081632</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="I5" t="n">
-        <v>5050</v>
+        <v>148</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>281</v>
+        <v>851</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N5" t="n">
-        <v>394</v>
+        <v>66</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X5" t="n">
-        <v>22.4</v>
+        <v>19.8319163664306</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.283524904214559</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.6203056614775</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1097,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1109,22 +1065,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>516</v>
+        <v>1109</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,121 +1081,114 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.09534185109131</v>
+        <v>79.1909800174918</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.3937263385613</v>
       </c>
       <c r="E6" t="n">
-        <v>29.0256076388888</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="I6" t="n">
-        <v>2800</v>
+        <v>173</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="K6" t="n">
-        <v>797</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>410</v>
+        <v>24</v>
       </c>
       <c r="M6" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1631</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="P6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>30.2393684746626</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>29.7425256555005</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.257839721254355</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.1464222052457</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>24.6143810163112</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2359</v>
+        <v>2121</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,79 +1196,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.26097786270191</v>
+        <v>82.77180653788631</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>23.0300453514739</v>
       </c>
       <c r="E7" t="n">
-        <v>24.2214532871972</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4510</v>
+        <v>56.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>67.3</v>
       </c>
       <c r="K7" t="n">
-        <v>376.3</v>
+        <v>123.9</v>
       </c>
       <c r="L7" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>320.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1475.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>89.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>272.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>22.8</v>
       </c>
       <c r="V7" t="n">
-        <v>37.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>22.5681181563535</v>
       </c>
       <c r="X7" t="n">
-        <v>24.35</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.314878892733564</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.5734657499363</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.6975361509812</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1344,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1353,24 +1295,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>136</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1378,77 +1309,79 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84.5302151304282</v>
+        <v>79.51356757167849</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E8" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>523</v>
+      </c>
+      <c r="I8" t="n">
+        <v>178</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>980</v>
       </c>
       <c r="L8" t="n">
-        <v>162.8</v>
+        <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>134.3</v>
+        <v>65</v>
       </c>
       <c r="N8" t="n">
-        <v>643.1</v>
+        <v>58</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>219</v>
       </c>
       <c r="P8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="V8" t="n">
-        <v>46.8</v>
+        <v>0.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X8" t="n">
-        <v>26.4</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.197952218430034</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>26.0831054612881</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1466,29 +1399,22 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1496,85 +1422,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.36462278500269</v>
+        <v>72.13777473572139</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>28.0890109547142</v>
       </c>
       <c r="E9" t="n">
-        <v>30.4271978579252</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>379</v>
       </c>
       <c r="I9" t="n">
-        <v>2040</v>
+        <v>491.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>284.9</v>
       </c>
       <c r="K9" t="n">
-        <v>78</v>
+        <v>1155.7</v>
       </c>
       <c r="L9" t="n">
-        <v>26.4</v>
+        <v>140.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>193.1</v>
       </c>
       <c r="N9" t="n">
-        <v>104.4</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>377.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>26.5151515151515</v>
       </c>
       <c r="X9" t="n">
-        <v>22.9</v>
+        <v>26.2096759585991</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.271698113207547</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.6736985933985</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1583,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -1595,24 +1521,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>570</v>
+        <v>633</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1620,40 +1537,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.10493763784319</v>
+        <v>82.8868868355008</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>37.4213957794838</v>
       </c>
       <c r="E10" t="n">
-        <v>31.2213039485766</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="I10" t="n">
-        <v>1180</v>
+        <v>63.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>165.6</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>416.5</v>
       </c>
       <c r="L10" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1671,34 +1588,34 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X10" t="n">
-        <v>27.2</v>
+        <v>24.856233988737</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.294670846394984</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>26.5066584133226</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1707,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1719,22 +1636,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>599</v>
+        <v>2397</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1742,85 +1652,85 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.724576013385</v>
+        <v>76.83366827642151</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>29.3847566574839</v>
       </c>
       <c r="E11" t="n">
-        <v>28.515625</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>818.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3870</v>
+        <v>45.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>9.9</v>
       </c>
       <c r="K11" t="n">
-        <v>307.1</v>
+        <v>873.8</v>
       </c>
       <c r="L11" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>87.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>739.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>55.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>24.5416348357525</v>
       </c>
       <c r="X11" t="n">
-        <v>24.05</v>
+        <v>24.4249070315066</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.113725490196078</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.3188184364655</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>24.152404368873</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1838,27 +1748,18 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>156</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>52806783</v>
+        <v>54691994</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1866,117 +1767,106 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>78.2559890485968</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>83.1457905544148</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34.7222222222222</v>
+      </c>
       <c r="E12" t="n">
-        <v>25.3934311203181</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>62</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>649</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>1054</v>
+        <v>99</v>
       </c>
       <c r="O12" t="n">
-        <v>547</v>
+        <v>274</v>
       </c>
       <c r="P12" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>26.1650726443076</v>
       </c>
       <c r="X12" t="n">
-        <v>27.7</v>
+        <v>25.25654394235911</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>595.1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>226</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>166</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54961732</v>
+        <v>51619206</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1984,74 +1874,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.21902806297059</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>85.9794661190965</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22.4058769513315</v>
+      </c>
       <c r="E13" t="n">
-        <v>27.170631566236</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>52</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>642</v>
+      </c>
+      <c r="I13" t="n">
+        <v>850</v>
+      </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1683</v>
+      </c>
+      <c r="L13" t="n">
+        <v>331</v>
+      </c>
+      <c r="M13" t="n">
+        <v>426</v>
+      </c>
+      <c r="N13" t="n">
+        <v>131</v>
+      </c>
       <c r="O13" t="n">
-        <v>548</v>
+        <v>888</v>
       </c>
       <c r="P13" t="n">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>583</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>1887</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>31.8</v>
       </c>
       <c r="V13" t="n">
-        <v>17</v>
+        <v>0.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>32.72225629969368</v>
       </c>
       <c r="X13" t="n">
-        <v>27.5</v>
+        <v>31.4390817069759</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>86.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>575.2</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2068,25 +1972,12 @@
       <c r="AI13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>165</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>160</v>
-      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54037816</v>
+        <v>55052657</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2094,71 +1985,77 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86.88569472963719</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>74.009582477755</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.1632653061225</v>
+      </c>
       <c r="E14" t="n">
-        <v>20.2865079117381</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55</v>
+      </c>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>291</v>
+      </c>
+      <c r="M14" t="n">
+        <v>358</v>
+      </c>
+      <c r="N14" t="n">
+        <v>193</v>
+      </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>842</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>23.55493157760051</v>
       </c>
       <c r="X14" t="n">
-        <v>24.7</v>
+        <v>22.84236339419522</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>78.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>468.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2179,24 +2076,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>206</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>52440331</v>
+        <v>52837261</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2204,82 +2092,88 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84.06297056810401</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>83.49623545516771</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29.0687732977668</v>
+      </c>
       <c r="E15" t="n">
-        <v>21.0076677987465</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="I15" t="n">
+        <v>307</v>
+      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>511</v>
       </c>
       <c r="K15" t="n">
-        <v>322</v>
+        <v>1054</v>
       </c>
       <c r="L15" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="M15" t="n">
-        <v>186</v>
+        <v>256</v>
       </c>
       <c r="N15" t="n">
-        <v>621</v>
+        <v>289</v>
       </c>
       <c r="O15" t="n">
-        <v>322</v>
+        <v>618</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>621</v>
+        <v>26</v>
       </c>
       <c r="S15" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>449</v>
+        <v>25</v>
       </c>
       <c r="V15" t="n">
-        <v>486</v>
+        <v>0.28</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>26.6107064849649</v>
       </c>
       <c r="X15" t="n">
-        <v>22.5</v>
+        <v>25.68147355921802</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>73.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>394.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2288,33 +2182,20 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>213</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>200</v>
-      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54555863</v>
+        <v>54037816</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2322,68 +2203,74 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>73.4236824093087</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>86.88569472963719</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20.2865079117381</v>
+      </c>
       <c r="E16" t="n">
-        <v>29.40778799351</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>34</v>
+      </c>
       <c r="O16" t="n">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="P16" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>25.0828190312827</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>24.41578904817543</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>482.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2392,35 +2279,30 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
+        <v>206</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53649976</v>
+        <v>54312439</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2428,81 +2310,77 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>86.93497604380561</v>
+        <v>81.3771389459274</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30.8248299319728</v>
       </c>
       <c r="E17" t="n">
-        <v>20.6427915518825</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>57</v>
+      </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>284</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>152</v>
+        <v>323</v>
       </c>
       <c r="M17" t="n">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="N17" t="n">
-        <v>618</v>
+        <v>162</v>
       </c>
       <c r="O17" t="n">
-        <v>284</v>
+        <v>734</v>
       </c>
       <c r="P17" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>25.84676275812381</v>
       </c>
       <c r="X17" t="n">
-        <v>22.6</v>
+        <v>25.44738950172107</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>76.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>435.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2522,25 +2400,12 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>162</v>
-      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53239344</v>
+        <v>52532268</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2548,75 +2413,79 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>73.7303216974675</v>
+        <v>78.1382614647502</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>29.4117647058824</v>
       </c>
       <c r="E18" t="n">
-        <v>24.4897959183673</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="K18" t="n">
-        <v>267</v>
+        <v>199</v>
       </c>
       <c r="L18" t="n">
-        <v>696</v>
+        <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>632</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>1595</v>
+        <v>49</v>
       </c>
       <c r="O18" t="n">
-        <v>221</v>
+        <v>133</v>
       </c>
       <c r="P18" t="n">
-        <v>639</v>
+        <v>46</v>
       </c>
       <c r="Q18" t="n">
-        <v>586</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1446</v>
+        <v>133</v>
       </c>
       <c r="S18" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="T18" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>470</v>
+        <v>28</v>
       </c>
       <c r="V18" t="n">
-        <v>662</v>
+        <v>0.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>29.76197435818443</v>
       </c>
       <c r="X18" t="n">
-        <v>26.6</v>
+        <v>27.89402598743426</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>82.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>536.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2628,39 +2497,30 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>251</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54836611</v>
+        <v>51310921</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2668,74 +2528,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>90.24503764544831</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>82.76796714579049</v>
+      </c>
+      <c r="D19" t="n">
+        <v>23.8086901719128</v>
+      </c>
       <c r="E19" t="n">
-        <v>30.8248299319728</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50</v>
+      </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>414</v>
+      </c>
+      <c r="I19" t="n">
+        <v>322</v>
+      </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="K19" t="n">
+        <v>986</v>
+      </c>
+      <c r="L19" t="n">
+        <v>414</v>
+      </c>
+      <c r="M19" t="n">
+        <v>322</v>
+      </c>
+      <c r="N19" t="n">
+        <v>221</v>
+      </c>
       <c r="O19" t="n">
-        <v>75</v>
+        <v>957</v>
       </c>
       <c r="P19" t="n">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>349</v>
+        <v>225</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>100</v>
+        <v>27.6</v>
       </c>
       <c r="V19" t="n">
-        <v>100</v>
+        <v>0.14</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>28.52056580206764</v>
       </c>
       <c r="X19" t="n">
-        <v>24.8</v>
+        <v>27.79113361913022</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>471.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2744,29 +2618,24 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
+        <v>182</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54898253</v>
+        <v>51795972</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2774,65 +2643,79 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>82.24777549623541</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>85.71663244353179</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30.0432622977087</v>
+      </c>
       <c r="E20" t="n">
-        <v>24.0054869684499</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>50</v>
+      </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>55</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>411</v>
+      </c>
+      <c r="I20" t="n">
+        <v>297</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="K20" t="n">
+        <v>921</v>
+      </c>
+      <c r="L20" t="n">
+        <v>175</v>
+      </c>
+      <c r="M20" t="n">
+        <v>114</v>
+      </c>
+      <c r="N20" t="n">
+        <v>130</v>
+      </c>
       <c r="O20" t="n">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="P20" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>968</v>
+        <v>9</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>28.42507283621251</v>
       </c>
       <c r="X20" t="n">
-        <v>21.1</v>
+        <v>27.825473350034</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>68.3</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>348.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2841,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2850,33 +2733,20 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>179</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>99</v>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52714540</v>
+        <v>54921492</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2884,86 +2754,80 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.2313483915127</v>
+        <v>74.8008213552361</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>30.5555555555556</v>
       </c>
       <c r="E21" t="n">
-        <v>30.7933824417341</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>60</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>402</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>175</v>
+        <v>415</v>
       </c>
       <c r="M21" t="n">
-        <v>256</v>
+        <v>713</v>
       </c>
       <c r="N21" t="n">
-        <v>833</v>
+        <v>289</v>
       </c>
       <c r="O21" t="n">
-        <v>402</v>
+        <v>1417</v>
       </c>
       <c r="P21" t="n">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V21" t="n">
-        <v>36</v>
+        <v>0.36</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>26.32422758739949</v>
       </c>
       <c r="X21" t="n">
-        <v>30.4</v>
+        <v>24.87045980339612</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>98.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>700.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2972,33 +2836,24 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>127</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>54513203</v>
+        <v>52588274</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3006,65 +2861,79 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>81.9466119096509</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>87.5674195756331</v>
+      </c>
+      <c r="D22" t="n">
+        <v>26.2975778546713</v>
+      </c>
       <c r="E22" t="n">
-        <v>23.6614386154678</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="I22" t="n">
+        <v>128</v>
+      </c>
       <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>462</v>
+      </c>
+      <c r="L22" t="n">
+        <v>251</v>
+      </c>
+      <c r="M22" t="n">
+        <v>128</v>
+      </c>
+      <c r="N22" t="n">
+        <v>83</v>
+      </c>
       <c r="O22" t="n">
-        <v>581</v>
+        <v>462</v>
       </c>
       <c r="P22" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1493</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>30.30310116469687</v>
       </c>
       <c r="X22" t="n">
-        <v>25.7</v>
+        <v>29.19428970270929</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>81.5</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>481.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3076,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3091,24 +2960,15 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53625077</v>
+        <v>53531320</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3116,81 +2976,85 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>77.242984257358</v>
+        <v>82.072553045859</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>23.4375</v>
       </c>
       <c r="E23" t="n">
-        <v>24.0979591836735</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45</v>
+      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="I23" t="n">
+        <v>337</v>
+      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="K23" t="n">
-        <v>562</v>
+        <v>663</v>
       </c>
       <c r="L23" t="n">
-        <v>518</v>
+        <v>175</v>
       </c>
       <c r="M23" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N23" t="n">
-        <v>1354</v>
+        <v>93</v>
       </c>
       <c r="O23" t="n">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="P23" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1347</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>59</v>
+        <v>24.8</v>
       </c>
       <c r="V23" t="n">
-        <v>59</v>
+        <v>0.22</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>25.91042473536056</v>
       </c>
       <c r="X23" t="n">
-        <v>29.8</v>
+        <v>24.89604407083738</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>97.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>702.1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3211,24 +3075,15 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>204</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>53513879</v>
+        <v>55595677</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3236,115 +3091,106 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.06023271731689</v>
+        <v>82.32717316906231</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>23.8884409806205</v>
       </c>
       <c r="E24" t="n">
-        <v>24.8109640831758</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40</v>
+      </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="n">
-        <v>50</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>498</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>32</v>
+        <v>227.91464</v>
       </c>
       <c r="M24" t="n">
-        <v>292</v>
+        <v>475.4452</v>
       </c>
       <c r="N24" t="n">
-        <v>822</v>
+        <v>137.97755</v>
       </c>
       <c r="O24" t="n">
-        <v>498</v>
+        <v>841.3373899999999</v>
       </c>
       <c r="P24" t="n">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="Q24" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>26.83374</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>27.94343178123009</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>27.03356292816895</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>85.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>541.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
+        <v>148</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51988931</v>
+        <v>52491057</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3352,72 +3198,88 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>78.52977412731011</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>77.95756331279949</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24.6913580246914</v>
+      </c>
       <c r="E25" t="n">
-        <v>34.0203461487647</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>49</v>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>184</v>
+      </c>
+      <c r="I25" t="n">
+        <v>91</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="K25" t="n">
+        <v>341</v>
+      </c>
+      <c r="L25" t="n">
+        <v>162</v>
+      </c>
+      <c r="M25" t="n">
+        <v>91</v>
+      </c>
+      <c r="N25" t="n">
+        <v>66</v>
+      </c>
       <c r="O25" t="n">
-        <v>578.4619</v>
+        <v>319</v>
       </c>
       <c r="P25" t="n">
-        <v>173.05403</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>212.97182</v>
+        <v>22</v>
       </c>
       <c r="R25" t="n">
-        <v>964.48785</v>
+        <v>55</v>
       </c>
       <c r="S25" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="T25" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="V25" t="n">
-        <v>154</v>
+        <v>0.24</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>28.80704469963306</v>
       </c>
       <c r="X25" t="n">
-        <v>26.933283</v>
+        <v>27.47319424673812</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>83.06091000000001</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>514.9822</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3434,25 +3296,12 @@
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>139</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>52482138</v>
+        <v>53532802</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3460,80 +3309,82 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>81.6563997262149</v>
+        <v>89.2457221081451</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>22.0384011592803</v>
       </c>
       <c r="E26" t="n">
-        <v>26.8135904499541</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="I26" t="n">
+        <v>639</v>
+      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="K26" t="n">
-        <v>408</v>
+        <v>1302</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="M26" t="n">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="N26" t="n">
-        <v>841</v>
+        <v>221</v>
       </c>
       <c r="O26" t="n">
-        <v>408</v>
+        <v>900</v>
       </c>
       <c r="P26" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="Q26" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>814</v>
+        <v>161</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>33</v>
+        <v>30.8</v>
       </c>
       <c r="V26" t="n">
-        <v>33</v>
+        <v>0.23</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>31.44901675495852</v>
       </c>
       <c r="X26" t="n">
-        <v>28.2</v>
+        <v>30.55595781765472</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>89.7</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>619.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3542,39 +3393,30 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>158</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>196</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>52803803</v>
+        <v>55005074</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3582,73 +3424,71 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>87.45516769336071</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>90.03422313483919</v>
+      </c>
+      <c r="D27" t="n">
+        <v>28.125</v>
+      </c>
       <c r="E27" t="n">
-        <v>19.2335607490202</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>55</v>
+      </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>134</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>311</v>
+        <v>177</v>
       </c>
       <c r="M27" t="n">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="N27" t="n">
-        <v>760</v>
+        <v>161</v>
       </c>
       <c r="O27" t="n">
-        <v>134</v>
+        <v>417</v>
       </c>
       <c r="P27" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>287</v>
+        <v>22</v>
       </c>
       <c r="V27" t="n">
-        <v>414</v>
+        <v>0.28</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>22.60000191904914</v>
       </c>
       <c r="X27" t="n">
-        <v>20.3</v>
+        <v>21.6401826367892</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>62.9</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>304.5</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3675,20 +3515,15 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
+        <v>135</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52718271</v>
+        <v>53568698</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3696,86 +3531,88 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>82.2368240930869</v>
+        <v>87.1841204654346</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>19.8838530488575</v>
       </c>
       <c r="E28" t="n">
-        <v>21.6712580348944</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>55</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="I28" t="n">
+        <v>222</v>
+      </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K28" t="n">
-        <v>269</v>
+        <v>568</v>
       </c>
       <c r="L28" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="M28" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="N28" t="n">
-        <v>345</v>
+        <v>230</v>
       </c>
       <c r="O28" t="n">
-        <v>68</v>
+        <v>431</v>
       </c>
       <c r="P28" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>28.36141085897575</v>
       </c>
       <c r="X28" t="n">
-        <v>23.9</v>
+        <v>27.11868656552212</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>80.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>486.3</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3793,20 +3630,15 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
+        <v>172</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>52082861</v>
+        <v>51407442</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3814,78 +3646,82 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>69.55509924709099</v>
+        <v>89.1006160164271</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>23.8894628099174</v>
       </c>
       <c r="E29" t="n">
-        <v>25.4766600920447</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>622</v>
+      </c>
+      <c r="I29" t="n">
+        <v>547</v>
+      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="K29" t="n">
-        <v>427</v>
+        <v>1508</v>
       </c>
       <c r="L29" t="n">
-        <v>968</v>
+        <v>594</v>
       </c>
       <c r="M29" t="n">
-        <v>430</v>
+        <v>509</v>
       </c>
       <c r="N29" t="n">
-        <v>1825</v>
+        <v>241</v>
       </c>
       <c r="O29" t="n">
-        <v>296</v>
+        <v>1344</v>
       </c>
       <c r="P29" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1251</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>30.5</v>
       </c>
       <c r="V29" t="n">
-        <v>25</v>
+        <v>0.37</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>31.79915762976069</v>
       </c>
       <c r="X29" t="n">
-        <v>24.1</v>
+        <v>30.39091913303852</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>79.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>461.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3894,35 +3730,30 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
+        <v>166</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>54260472</v>
+        <v>54686077</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3930,79 +3761,83 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>89.5222450376454</v>
+        <v>74.97056810403831</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>34.6260387811634</v>
       </c>
       <c r="E30" t="n">
-        <v>22.65625</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>59</v>
+      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="n">
-        <v>67</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>883</v>
+      </c>
+      <c r="M30" t="n">
+        <v>284</v>
+      </c>
+      <c r="N30" t="n">
+        <v>570</v>
+      </c>
       <c r="O30" t="n">
-        <v>50</v>
+        <v>1737</v>
       </c>
       <c r="P30" t="n">
-        <v>207</v>
+        <v>351</v>
       </c>
       <c r="Q30" t="n">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>493</v>
+        <v>31</v>
       </c>
       <c r="S30" t="n">
-        <v>150</v>
+        <v>396</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="V30" t="n">
-        <v>150</v>
+        <v>0.32</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>29.60281941509253</v>
       </c>
       <c r="X30" t="n">
-        <v>24.3</v>
+        <v>27.80029502818709</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>483.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4011,30 +3846,21 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>203</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52830899</v>
+        <v>52698831</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4042,82 +3868,88 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84.5284052019165</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>80.1286789869952</v>
+      </c>
+      <c r="D31" t="n">
+        <v>31.561671506123</v>
+      </c>
       <c r="E31" t="n">
-        <v>20.338326446281</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>45</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>614</v>
+      </c>
+      <c r="I31" t="n">
+        <v>229</v>
+      </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="K31" t="n">
-        <v>194</v>
+        <v>978</v>
       </c>
       <c r="L31" t="n">
-        <v>193</v>
+        <v>614</v>
       </c>
       <c r="M31" t="n">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="N31" t="n">
-        <v>540</v>
+        <v>124</v>
       </c>
       <c r="O31" t="n">
-        <v>129</v>
+        <v>936</v>
       </c>
       <c r="P31" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>28.83887568825143</v>
       </c>
       <c r="X31" t="n">
-        <v>25.8</v>
+        <v>27.43841363493709</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>83.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>515.5</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4126,29 +3958,20 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53525860</v>
+        <v>51798345</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4156,119 +3979,114 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>77.92197125256671</v>
+        <v>80.78850102669399</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>25.8264462809917</v>
       </c>
       <c r="E32" t="n">
-        <v>32.0461464508893</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>45</v>
+      </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>55</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="I32" t="n">
+        <v>241</v>
+      </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="M32" t="n">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="N32" t="n">
-        <v>125</v>
+        <v>492</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>1132</v>
       </c>
       <c r="P32" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>30.74873500535418</v>
       </c>
       <c r="X32" t="n">
-        <v>24.3</v>
+        <v>29.03905216218495</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>145</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>51756764</v>
+        <v>53324217</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4276,121 +4094,114 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>70.72416153319639</v>
+        <v>78.8227241615332</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>25.3515413737155</v>
       </c>
       <c r="E33" t="n">
-        <v>20.8209399167162</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>55</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>284</v>
+      </c>
+      <c r="I33" t="n">
+        <v>215</v>
+      </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="K33" t="n">
-        <v>495</v>
+        <v>666</v>
       </c>
       <c r="L33" t="n">
-        <v>1030</v>
+        <v>284</v>
       </c>
       <c r="M33" t="n">
-        <v>778</v>
+        <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>2304</v>
+        <v>93</v>
       </c>
       <c r="O33" t="n">
-        <v>318</v>
+        <v>419</v>
       </c>
       <c r="P33" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1017</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>16</v>
+        <v>26.9</v>
       </c>
       <c r="V33" t="n">
-        <v>346</v>
+        <v>0.28</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>27.02450933700383</v>
       </c>
       <c r="X33" t="n">
-        <v>23.4</v>
+        <v>25.9134431500973</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>73.8</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>404.5</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>52310176</v>
+        <v>55741033</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4398,82 +4209,80 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>75.28815879534569</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>83.7070499657769</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24.3910588392529</v>
+      </c>
       <c r="E34" t="n">
-        <v>23.8894628099174</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40</v>
+      </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>897</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>324</v>
+        <v>247.90067</v>
       </c>
       <c r="M34" t="n">
-        <v>359</v>
+        <v>155.37279</v>
       </c>
       <c r="N34" t="n">
-        <v>1580</v>
+        <v>74.98457999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>516</v>
+        <v>478.25804</v>
       </c>
       <c r="P34" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>761</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>123</v>
+        <v>24.610813</v>
       </c>
       <c r="V34" t="n">
-        <v>123</v>
+        <v>0.26</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>25.50066760197503</v>
       </c>
       <c r="X34" t="n">
-        <v>26.6</v>
+        <v>24.78873424054342</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4482,33 +4291,24 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>168</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>198</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51180546</v>
+        <v>52505349</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4516,113 +4316,114 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.9452429842574</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>85.02943189596169</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28.0816326530612</v>
+      </c>
       <c r="E35" t="n">
-        <v>25.3443526170799</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>55</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>72</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>904</v>
+      </c>
+      <c r="I35" t="n">
+        <v>422</v>
+      </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>238</v>
+        <v>1426</v>
       </c>
       <c r="L35" t="n">
-        <v>178</v>
+        <v>587</v>
       </c>
       <c r="M35" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N35" t="n">
-        <v>526</v>
+        <v>98</v>
       </c>
       <c r="O35" t="n">
-        <v>210</v>
+        <v>794</v>
       </c>
       <c r="P35" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>43</v>
+        <v>24.8</v>
       </c>
       <c r="V35" t="n">
-        <v>43</v>
+        <v>0.27</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>26.29239659878111</v>
       </c>
       <c r="X35" t="n">
-        <v>23</v>
+        <v>25.43988326602312</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>410.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51375337</v>
+        <v>55801471</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4630,73 +4431,71 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>81.3716632443532</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>85.6919917864476</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24.8357634994392</v>
+      </c>
       <c r="E36" t="n">
-        <v>25.3515413737155</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>55</v>
+      </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
-        <v>55</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>840</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>611</v>
+        <v>416.9676</v>
       </c>
       <c r="M36" t="n">
-        <v>483</v>
+        <v>43.30304</v>
       </c>
       <c r="N36" t="n">
-        <v>1933</v>
+        <v>90.67731000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>871</v>
+        <v>550.94795</v>
       </c>
       <c r="P36" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1652</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>22.331718</v>
       </c>
       <c r="V36" t="n">
-        <v>76</v>
+        <v>0.16</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>23.18422151795314</v>
       </c>
       <c r="X36" t="n">
-        <v>29.9</v>
+        <v>22.68329367185157</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>683.9</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -4723,24 +4522,15 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>207</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>102</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51789547</v>
+        <v>51770251</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4748,89 +4538,91 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>88.6488706365503</v>
+        <v>82.9815195071869</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>33.425160697888</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2975778546713</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>55</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>1584</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1198</v>
+      </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>1543</v>
       </c>
       <c r="K37" t="n">
-        <v>869</v>
+        <v>4325</v>
       </c>
       <c r="L37" t="n">
-        <v>357</v>
+        <v>1713</v>
       </c>
       <c r="M37" t="n">
-        <v>395</v>
+        <v>1236</v>
       </c>
       <c r="N37" t="n">
-        <v>1621</v>
+        <v>1565</v>
       </c>
       <c r="O37" t="n">
-        <v>860</v>
+        <v>4514</v>
       </c>
       <c r="P37" t="n">
-        <v>349</v>
+        <v>254</v>
       </c>
       <c r="Q37" t="n">
-        <v>335</v>
+        <v>9</v>
       </c>
       <c r="R37" t="n">
-        <v>1544</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>563</v>
+        <v>263</v>
       </c>
       <c r="T37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>777</v>
+        <v>27.7</v>
       </c>
       <c r="V37" t="n">
-        <v>1350</v>
+        <v>0.23</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>28.42507283621251</v>
       </c>
       <c r="X37" t="n">
-        <v>31.9</v>
+        <v>27.66485659352505</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>102.5</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>771.5</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -4844,17 +4636,8 @@
       <c r="AI37" t="n">
         <v>0</v>
       </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
